--- a/Staff_Contacts_Final.xlsx
+++ b/Staff_Contacts_Final.xlsx
@@ -127,7 +127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -149,11 +149,55 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -203,6 +247,8 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -665,6 +711,19 @@
           <t xml:space="preserve">  Church  ·  30 staff</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="17" t="n"/>
+      <c r="N2" s="18" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -707,7 +766,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>alinealvesbarbosa</t>
+          <t>@alinealvesbarbosa</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -765,7 +824,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>BethanyRoach</t>
+          <t>@BethanyRoach</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -823,7 +882,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Boromey_hom</t>
+          <t>@Boromey_hom</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -881,7 +940,7 @@
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>chompavong</t>
+          <t>@chompavong</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -939,7 +998,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>danathy</t>
+          <t>@danathy</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -997,7 +1056,7 @@
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>davitmao</t>
+          <t>@davitmao</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1051,7 +1110,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>EddieRoach</t>
+          <t>@EddieRoach</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1109,7 +1168,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Ellie_Weber</t>
+          <t>@Ellie_Weber</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1167,7 +1226,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>kanal_tensok</t>
+          <t>@kanal_tensok</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1279,7 +1338,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Kalimom</t>
+          <t>@Kalimom</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1341,7 +1400,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>noanoemi</t>
+          <t>@noanoemi</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1392,7 +1451,11 @@
           <t>panha.neang@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>+85577540537</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1446,10 +1509,14 @@
           <t>pichey.ken@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>+855969390522</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>pichey16</t>
+          <t>@pichey16</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1504,10 +1571,14 @@
           <t>ranaomi.heak@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>+85512611517</t>
+        </is>
+      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Naomi_Heak</t>
+          <t>@Naomi_Heak</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1554,10 +1625,14 @@
           <t>rany.mom@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>+85512668091</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>RanyMom</t>
+          <t>@RanyMom</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1612,10 +1687,14 @@
           <t>robson.barbosa@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>+855963633843</t>
+        </is>
+      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>RobsonICF</t>
+          <t>@RobsonICF</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1669,7 +1748,7 @@
       <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Rothanaros</t>
+          <t>@Rothanaros</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1724,10 +1803,14 @@
           <t>ryna.mom@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>+85585221991</t>
+        </is>
+      </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>RynaMom</t>
+          <t>@RynaMom</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1785,7 +1868,7 @@
       <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>sambathsong</t>
+          <t>@sambathsong</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1847,7 +1930,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Seanglyleng</t>
+          <t>@Seanglyleng</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1902,10 +1985,14 @@
           <t>sombo.ros@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>+85512668092</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>somboros</t>
+          <t>@somboros</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1967,7 +2054,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>YEMSOMOUN</t>
+          <t>@YEMSOMOUN</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2025,7 +2112,7 @@
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Vat_Sopheak</t>
+          <t>@Vat_Sopheak</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2087,7 +2174,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>NgatSopheap</t>
+          <t>@NgatSopheap</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2149,7 +2236,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>sotheavy_ngen</t>
+          <t>@sotheavy_ngen</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2207,7 +2294,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>sovansreyreach</t>
+          <t>@sovansreyreach</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2269,7 +2356,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Roussreileak</t>
+          <t>@Roussreileak</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2331,7 +2418,7 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>SreyPich99</t>
+          <t>@SreyPich99</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2408,6 +2495,19 @@
           <t xml:space="preserve">  Catering  ·  5 staff</t>
         </is>
       </c>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
+      <c r="L33" s="17" t="n"/>
+      <c r="M33" s="17" t="n"/>
+      <c r="N33" s="18" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="n">
@@ -2442,7 +2542,7 @@
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>bophamom</t>
+          <t>@bophamom</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2494,7 +2594,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>@HuonLieng</t>
+        </is>
+      </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>06-Jul</t>
@@ -2546,7 +2650,7 @@
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>pechsang</t>
+          <t>@pechsang</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2646,7 +2750,7 @@
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>somchhang</t>
+          <t>@somchhang</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2673,6 +2777,19 @@
           <t xml:space="preserve">  Donor Care  ·  6 staff</t>
         </is>
       </c>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
+      <c r="L39" s="17" t="n"/>
+      <c r="M39" s="17" t="n"/>
+      <c r="N39" s="18" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="n">
@@ -2708,10 +2825,14 @@
           <t>jane.meas@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>+855968958086</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>jane_meas</t>
+          <t>@jane_meas</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2769,7 +2890,7 @@
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Koukkongkea</t>
+          <t>@Koukkongkea</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2824,10 +2945,14 @@
           <t>longsamnieng.pol@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>+85517777039</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Samniengpol</t>
+          <t>@Samniengpol</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2885,7 +3010,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>NDstrupler</t>
+          <t>@NDstrupler</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2939,7 +3064,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>rebeccavey</t>
+          <t>@rebeccavey</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr"/>
@@ -2985,7 +3110,7 @@
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Ornsreyleak</t>
+          <t>@Ornsreyleak</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3012,6 +3137,19 @@
           <t xml:space="preserve">  Guest Relations  ·  3 staff</t>
         </is>
       </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+      <c r="G46" s="17" t="n"/>
+      <c r="H46" s="17" t="n"/>
+      <c r="I46" s="17" t="n"/>
+      <c r="J46" s="17" t="n"/>
+      <c r="K46" s="17" t="n"/>
+      <c r="L46" s="17" t="n"/>
+      <c r="M46" s="17" t="n"/>
+      <c r="N46" s="18" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -3043,10 +3181,14 @@
           <t>sambo.hout@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>+85512668061</t>
+        </is>
+      </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Sambohout</t>
+          <t>@Sambohout</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3100,7 +3242,7 @@
       <c r="H48" s="4" t="inlineStr"/>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>SophieeHann</t>
+          <t>@SophieeHann</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3162,7 +3304,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>steffilendi</t>
+          <t>@steffilendi</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3185,6 +3327,19 @@
           <t xml:space="preserve">  Human Resources  ·  4 staff</t>
         </is>
       </c>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
+      <c r="G50" s="17" t="n"/>
+      <c r="H50" s="17" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
+      <c r="L50" s="17" t="n"/>
+      <c r="M50" s="17" t="n"/>
+      <c r="N50" s="18" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -3227,7 +3382,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>nuthida_han</t>
+          <t>@nuthida_han</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3289,7 +3444,7 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>sodalinthangham</t>
+          <t>@sodalinthangham</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3347,7 +3502,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>thavytham</t>
+          <t>@thavytham</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3409,7 +3564,7 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>vivianstumpf</t>
+          <t>@vivianstumpf</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3432,6 +3587,19 @@
           <t xml:space="preserve">  MarCom  ·  8 staff</t>
         </is>
       </c>
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="17" t="n"/>
+      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="17" t="n"/>
+      <c r="I55" s="17" t="n"/>
+      <c r="J55" s="17" t="n"/>
+      <c r="K55" s="17" t="n"/>
+      <c r="L55" s="17" t="n"/>
+      <c r="M55" s="17" t="n"/>
+      <c r="N55" s="18" t="n"/>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="n">
@@ -3466,7 +3634,7 @@
       <c r="H56" s="4" t="inlineStr"/>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>florinflammer</t>
+          <t>@florinflammer</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3520,7 +3688,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>RatanaKhy</t>
+          <t>@RatanaKhy</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3571,10 +3739,14 @@
           <t>rayu.roeun@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>+855717506500</t>
+        </is>
+      </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>rayngu</t>
+          <t>@rayngu</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3632,7 +3804,7 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>savannss</t>
+          <t>@savannss</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3686,7 +3858,7 @@
       <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>SenglyM</t>
+          <t>@SenglyM</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3744,7 +3916,7 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>TannSokTheavy</t>
+          <t>@TannSokTheavy</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -3794,7 +3966,7 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>StephanieShelow</t>
+          <t>@StephanieShelow</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -3848,7 +4020,7 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>VuthaKry</t>
+          <t>@VuthaKry</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -3871,6 +4043,19 @@
           <t xml:space="preserve">  Operations  ·  7 staff</t>
         </is>
       </c>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="F64" s="17" t="n"/>
+      <c r="G64" s="17" t="n"/>
+      <c r="H64" s="17" t="n"/>
+      <c r="I64" s="17" t="n"/>
+      <c r="J64" s="17" t="n"/>
+      <c r="K64" s="17" t="n"/>
+      <c r="L64" s="17" t="n"/>
+      <c r="M64" s="17" t="n"/>
+      <c r="N64" s="18" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="3" t="n">
@@ -3952,8 +4137,16 @@
           <t>makara.tes@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>+85595455664</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>@tesmakara</t>
+        </is>
+      </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
           <t>17-Oct</t>
@@ -4006,10 +4199,14 @@
           <t>neaksen.sok@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>+85599267722</t>
+        </is>
+      </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>neksensok</t>
+          <t>@neksensok</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -4060,10 +4257,14 @@
           <t>sakorun.pok@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>+85512323925</t>
+        </is>
+      </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>Sakhoeun</t>
+          <t>@Sakhoeun</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -4114,10 +4315,14 @@
           <t>sreymom.lim@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>+85592200309</t>
+        </is>
+      </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Sreymomlim</t>
+          <t>@Sreymomlim</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -4179,7 +4384,7 @@
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>VanthenKim</t>
+          <t>@VanthenKim</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -4237,7 +4442,7 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Vatteychhun</t>
+          <t>@Vatteychhun</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4264,6 +4469,19 @@
           <t xml:space="preserve">  Property  ·  19 staff</t>
         </is>
       </c>
+      <c r="B72" s="17" t="n"/>
+      <c r="C72" s="17" t="n"/>
+      <c r="D72" s="17" t="n"/>
+      <c r="E72" s="17" t="n"/>
+      <c r="F72" s="17" t="n"/>
+      <c r="G72" s="17" t="n"/>
+      <c r="H72" s="17" t="n"/>
+      <c r="I72" s="17" t="n"/>
+      <c r="J72" s="17" t="n"/>
+      <c r="K72" s="17" t="n"/>
+      <c r="L72" s="17" t="n"/>
+      <c r="M72" s="17" t="n"/>
+      <c r="N72" s="18" t="n"/>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="3" t="n">
@@ -4302,7 +4520,7 @@
       <c r="H73" s="4" t="inlineStr"/>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>SoeurmBarang</t>
+          <t>@SoeurmBarang</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -4472,7 +4690,7 @@
       <c r="H76" s="4" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>loebhin</t>
+          <t>@loebhin</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -4530,7 +4748,7 @@
       <c r="H77" s="4" t="inlineStr"/>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>HingHoeun</t>
+          <t>@HingHoeun</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -4585,10 +4803,14 @@
           <t>hou.sokcheat@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>+85592220010</t>
+        </is>
+      </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>socheathour25</t>
+          <t>@socheathour25</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -4642,7 +4864,7 @@
       <c r="H79" s="4" t="inlineStr"/>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Sopheapkim</t>
+          <t>@Sopheapkim</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -4702,7 +4924,11 @@
           <t>+85585685335</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>@Kimsorn_Soeuth</t>
+        </is>
+      </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
           <t>18-Jul</t>
@@ -4754,7 +4980,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Martinstrupler</t>
+          <t>@Martinstrupler</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -4808,7 +5034,7 @@
       <c r="H82" s="4" t="inlineStr"/>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>HounNan</t>
+          <t>@HounNan</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -4866,7 +5092,7 @@
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>david_nhoem</t>
+          <t>@david_nhoem</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -4917,7 +5143,11 @@
           <t>rin.nga@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>+85517504093</t>
+        </is>
+      </c>
       <c r="I84" s="4" t="inlineStr"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -4978,7 +5208,7 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>sarathsok</t>
+          <t>@sarathsok</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -5144,7 +5374,7 @@
       <c r="H88" s="4" t="inlineStr"/>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>SilaKun</t>
+          <t>@SilaKun</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -5206,7 +5436,7 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>sopheapput</t>
+          <t>@sopheapput</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -5341,6 +5571,19 @@
           <t xml:space="preserve">  Social  ·  48 staff</t>
         </is>
       </c>
+      <c r="B92" s="17" t="n"/>
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="17" t="n"/>
+      <c r="E92" s="17" t="n"/>
+      <c r="F92" s="17" t="n"/>
+      <c r="G92" s="17" t="n"/>
+      <c r="H92" s="17" t="n"/>
+      <c r="I92" s="17" t="n"/>
+      <c r="J92" s="17" t="n"/>
+      <c r="K92" s="17" t="n"/>
+      <c r="L92" s="17" t="n"/>
+      <c r="M92" s="17" t="n"/>
+      <c r="N92" s="18" t="n"/>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -5376,10 +5619,14 @@
           <t>champa.toch@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr"/>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>+85592200379</t>
+        </is>
+      </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>ChampaTOCH</t>
+          <t>@ChampaTOCH</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -5437,7 +5684,7 @@
       <c r="H94" s="4" t="inlineStr"/>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>ChamroenMuon</t>
+          <t>@ChamroenMuon</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -5499,7 +5746,7 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>leatchanthat</t>
+          <t>@leatchanthat</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5553,7 +5800,7 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>barvchenda17</t>
+          <t>@barvchenda17</t>
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr"/>
@@ -5603,7 +5850,7 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>david_piseth</t>
+          <t>@david_piseth</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -5661,7 +5908,7 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Hana_seab</t>
+          <t>@Hana_seab</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr"/>
@@ -5711,7 +5958,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>KanhaUn</t>
+          <t>@KanhaUn</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -5765,7 +6012,7 @@
       <c r="H100" s="4" t="inlineStr"/>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>KaranoChhuon</t>
+          <t>@KaranoChhuon</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -5827,7 +6074,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>Khunhy</t>
+          <t>@Khunhy</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -5882,8 +6129,16 @@
           <t>kolap.touch@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>+85592200365</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>@TKolap</t>
+        </is>
+      </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
           <t>05-Oct</t>
@@ -5932,10 +6187,14 @@
           <t>kropumkannika.gnorng@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>+855716968338</t>
+        </is>
+      </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Kropumkannika</t>
+          <t>@Kropumkannika</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -5991,7 +6250,11 @@
           <t>+855962202122</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>@Makara_SG</t>
+        </is>
+      </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
           <t>01-Jan</t>
@@ -6097,7 +6360,7 @@
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>matthiaslendi</t>
+          <t>@matthiaslendi</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -6155,7 +6418,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Nirornsok</t>
+          <t>@Nirornsok</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -6217,7 +6480,7 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>Noya777</t>
+          <t>@Noya777</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -6271,7 +6534,7 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Ousaphealim</t>
+          <t>@Ousaphealim</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -6326,10 +6589,14 @@
           <t>parigna.souem@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr"/>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>+85592220026</t>
+        </is>
+      </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>Parignasouem</t>
+          <t>@Parignasouem</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -6391,7 +6658,7 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>tebphin</t>
+          <t>@tebphin</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -6445,7 +6712,7 @@
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>NovRina</t>
+          <t>@NovRina</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
@@ -6507,7 +6774,7 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>chamroeunrongroeung</t>
+          <t>@chamroeunrongroeung</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -6615,7 +6882,7 @@
       <c r="H115" s="4" t="inlineStr"/>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>savryklot</t>
+          <t>@savryklot</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -6677,7 +6944,7 @@
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>Seavykhean</t>
+          <t>@Seavykhean</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
@@ -6732,10 +6999,14 @@
           <t>seyla.nga@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>+85589577205</t>
+        </is>
+      </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>NgaSeyla</t>
+          <t>@NgaSeyla</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -6843,7 +7114,7 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>SimoneVivianneStrupler</t>
+          <t>@SimoneVivianneStrupler</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -6894,10 +7165,14 @@
           <t>sokuntheary.sim@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr"/>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>+85592200340</t>
+        </is>
+      </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>Sokuntheary</t>
+          <t>@Sokuntheary</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -6955,7 +7230,7 @@
       <c r="H121" s="4" t="inlineStr"/>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>maksophea</t>
+          <t>@maksophea</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -7013,7 +7288,7 @@
       <c r="H122" s="4" t="inlineStr"/>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>Pheaktra_M</t>
+          <t>@Pheaktra_M</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -7064,7 +7339,11 @@
           <t>sopheap.heang@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>+85512472698</t>
+        </is>
+      </c>
       <c r="I123" s="4" t="inlineStr"/>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -7183,7 +7462,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>Ngeun_Sotheany</t>
+          <t>@Ngeun_Sotheany</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -7238,10 +7517,14 @@
           <t>sotheavy.thea@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>+85568908604</t>
+        </is>
+      </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>Sotheavythea</t>
+          <t>@Sotheavythea</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
@@ -7292,10 +7575,14 @@
           <t>sothiery.un@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H127" s="4" t="inlineStr"/>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>+85581698902</t>
+        </is>
+      </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>Sothiery</t>
+          <t>@Sothiery</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -7353,7 +7640,7 @@
       <c r="H128" s="4" t="inlineStr"/>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>sreyrothouth</t>
+          <t>@sreyrothouth</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
@@ -7407,7 +7694,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>sreyleakso</t>
+          <t>@sreyleakso</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -7465,7 +7752,7 @@
       <c r="H130" s="4" t="inlineStr"/>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Sreymomthorng</t>
+          <t>@Sreymomthorng</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -7520,10 +7807,14 @@
           <t>sopheap.touch@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>+85577992321</t>
+        </is>
+      </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>SreymomTOUCH</t>
+          <t>@SreymomTOUCH</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -7585,7 +7876,7 @@
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>sreynouchkhit</t>
+          <t>@sreynouchkhit</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
@@ -7636,10 +7927,14 @@
           <t>sreypeou.hout@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H133" s="4" t="inlineStr"/>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>+85569467404</t>
+        </is>
+      </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>HoutSreyPov</t>
+          <t>@HoutSreyPov</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -7697,7 +7992,7 @@
       <c r="H134" s="4" t="inlineStr"/>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>sreytom2</t>
+          <t>@sreytom2</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
@@ -7752,10 +8047,14 @@
           <t>su.sey@icf-cambodia.com</t>
         </is>
       </c>
-      <c r="H135" s="4" t="inlineStr"/>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>+855965011489</t>
+        </is>
+      </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>Sey_Su</t>
+          <t>@Sey_Su</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -7813,7 +8112,7 @@
       <c r="H136" s="4" t="inlineStr"/>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>Thearithkeo</t>
+          <t>@Thearithkeo</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
@@ -7871,7 +8170,7 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>Tola_Khem</t>
+          <t>@Tola_Khem</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -7929,7 +8228,7 @@
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>vannrotha</t>
+          <t>@vannrotha</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
@@ -7987,7 +8286,7 @@
       <c r="H139" s="4" t="inlineStr"/>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>vicheakhen</t>
+          <t>@vicheakhen</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -8045,7 +8344,7 @@
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>vichethsong</t>
+          <t>@vichethsong</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
@@ -8072,6 +8371,19 @@
           <t xml:space="preserve">  Scholarship  ·  17 staff</t>
         </is>
       </c>
+      <c r="B141" s="17" t="n"/>
+      <c r="C141" s="17" t="n"/>
+      <c r="D141" s="17" t="n"/>
+      <c r="E141" s="17" t="n"/>
+      <c r="F141" s="17" t="n"/>
+      <c r="G141" s="17" t="n"/>
+      <c r="H141" s="17" t="n"/>
+      <c r="I141" s="17" t="n"/>
+      <c r="J141" s="17" t="n"/>
+      <c r="K141" s="17" t="n"/>
+      <c r="L141" s="17" t="n"/>
+      <c r="M141" s="17" t="n"/>
+      <c r="N141" s="18" t="n"/>
     </row>
     <row r="142" ht="16" customHeight="1">
       <c r="A142" s="5" t="n">
@@ -8102,7 +8414,7 @@
       <c r="H142" s="6" t="inlineStr"/>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>chhaivor</t>
+          <t>@chhaivor</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr"/>
@@ -8216,7 +8528,7 @@
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>CHY_MAKARA290106</t>
+          <t>@CHY_MAKARA290106</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr"/>
@@ -8258,7 +8570,7 @@
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>Nyrorth</t>
+          <t>@Nyrorth</t>
         </is>
       </c>
       <c r="J146" s="6" t="inlineStr"/>
@@ -8296,7 +8608,7 @@
       <c r="H147" s="6" t="inlineStr"/>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>RothNaroth</t>
+          <t>@RothNaroth</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr"/>
@@ -8406,7 +8718,7 @@
       <c r="H150" s="6" t="inlineStr"/>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>Sary_sarin</t>
+          <t>@Sary_sarin</t>
         </is>
       </c>
       <c r="J150" s="6" t="inlineStr"/>
@@ -8444,7 +8756,7 @@
       <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>Sintna12345</t>
+          <t>@Sintna12345</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr"/>
@@ -8486,7 +8798,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>Sopheakphol</t>
+          <t>@Sopheakphol</t>
         </is>
       </c>
       <c r="J152" s="6" t="inlineStr"/>
@@ -8524,7 +8836,7 @@
       <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>SotheaThov</t>
+          <t>@SotheaThov</t>
         </is>
       </c>
       <c r="J153" s="6" t="inlineStr"/>
@@ -8566,7 +8878,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>choeutsovann</t>
+          <t>@choeutsovann</t>
         </is>
       </c>
       <c r="J154" s="6" t="inlineStr"/>
@@ -8608,7 +8920,7 @@
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>Sreyleakhounn</t>
+          <t>@Sreyleakhounn</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr"/>
@@ -8688,7 +9000,7 @@
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>SreynuchPhuk</t>
+          <t>@SreynuchPhuk</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr"/>
@@ -8730,7 +9042,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>SreydavNak</t>
+          <t>@SreydavNak</t>
         </is>
       </c>
       <c r="J158" s="6" t="inlineStr"/>
@@ -8745,6 +9057,19 @@
           <t xml:space="preserve">  Leadership  ·  1 staff</t>
         </is>
       </c>
+      <c r="B159" s="17" t="n"/>
+      <c r="C159" s="17" t="n"/>
+      <c r="D159" s="17" t="n"/>
+      <c r="E159" s="17" t="n"/>
+      <c r="F159" s="17" t="n"/>
+      <c r="G159" s="17" t="n"/>
+      <c r="H159" s="17" t="n"/>
+      <c r="I159" s="17" t="n"/>
+      <c r="J159" s="17" t="n"/>
+      <c r="K159" s="17" t="n"/>
+      <c r="L159" s="17" t="n"/>
+      <c r="M159" s="17" t="n"/>
+      <c r="N159" s="18" t="n"/>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="3" t="n">
@@ -8783,7 +9108,7 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>SophalStrupler</t>
+          <t>@SophalStrupler</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
@@ -8806,6 +9131,19 @@
           <t xml:space="preserve">  New Campus  ·  1 staff</t>
         </is>
       </c>
+      <c r="B161" s="17" t="n"/>
+      <c r="C161" s="17" t="n"/>
+      <c r="D161" s="17" t="n"/>
+      <c r="E161" s="17" t="n"/>
+      <c r="F161" s="17" t="n"/>
+      <c r="G161" s="17" t="n"/>
+      <c r="H161" s="17" t="n"/>
+      <c r="I161" s="17" t="n"/>
+      <c r="J161" s="17" t="n"/>
+      <c r="K161" s="17" t="n"/>
+      <c r="L161" s="17" t="n"/>
+      <c r="M161" s="17" t="n"/>
+      <c r="N161" s="18" t="n"/>
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="3" t="n">
@@ -8844,7 +9182,7 @@
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>anninahuembeli</t>
+          <t>@anninahuembeli</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
@@ -8973,6 +9311,18 @@
           <t xml:space="preserve">  After School  ·  1 staff</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="18" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -9021,6 +9371,18 @@
           <t xml:space="preserve">  Education  ·  14 staff</t>
         </is>
       </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="17" t="n"/>
+      <c r="H4" s="17" t="n"/>
+      <c r="I4" s="17" t="n"/>
+      <c r="J4" s="17" t="n"/>
+      <c r="K4" s="17" t="n"/>
+      <c r="L4" s="17" t="n"/>
+      <c r="M4" s="18" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -9802,6 +10164,18 @@
           <t xml:space="preserve">  Family Care  ·  25 staff</t>
         </is>
       </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="17" t="n"/>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n"/>
+      <c r="M19" s="18" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -11094,6 +11468,18 @@
           <t xml:space="preserve">  Social  ·  8 staff</t>
         </is>
       </c>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="17" t="n"/>
+      <c r="H45" s="17" t="n"/>
+      <c r="I45" s="17" t="n"/>
+      <c r="J45" s="17" t="n"/>
+      <c r="K45" s="17" t="n"/>
+      <c r="L45" s="17" t="n"/>
+      <c r="M45" s="18" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="n">
@@ -12372,6 +12758,18 @@
           <t xml:space="preserve">  Church  ·  1 staff</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="18" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -12432,6 +12830,18 @@
           <t xml:space="preserve">  Kids  ·  7 staff</t>
         </is>
       </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="17" t="n"/>
+      <c r="H4" s="17" t="n"/>
+      <c r="I4" s="17" t="n"/>
+      <c r="J4" s="17" t="n"/>
+      <c r="K4" s="17" t="n"/>
+      <c r="L4" s="17" t="n"/>
+      <c r="M4" s="18" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -12810,6 +13220,18 @@
           <t xml:space="preserve">  Next Steps  ·  3 staff</t>
         </is>
       </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="18" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -12968,6 +13390,18 @@
           <t xml:space="preserve">  Outreach  ·  7 staff</t>
         </is>
       </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="17" t="n"/>
+      <c r="J16" s="17" t="n"/>
+      <c r="K16" s="17" t="n"/>
+      <c r="L16" s="17" t="n"/>
+      <c r="M16" s="18" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -13342,6 +13776,18 @@
           <t xml:space="preserve">  Worship  ·  4 staff</t>
         </is>
       </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="17" t="n"/>
+      <c r="L24" s="17" t="n"/>
+      <c r="M24" s="18" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -13569,6 +14015,18 @@
           <t xml:space="preserve">  Worship &amp; Technical  ·  4 staff</t>
         </is>
       </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n"/>
+      <c r="M29" s="18" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -13796,6 +14254,18 @@
           <t xml:space="preserve">  Youth  ·  2 staff</t>
         </is>
       </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17" t="n"/>
+      <c r="L34" s="17" t="n"/>
+      <c r="M34" s="18" t="n"/>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="n">
@@ -13913,6 +14383,18 @@
           <t xml:space="preserve">  Church  ·  2 staff</t>
         </is>
       </c>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n"/>
+      <c r="M37" s="18" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -14449,6 +14931,18 @@
           <t xml:space="preserve">  Fundraising  ·  5 staff</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="18" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -14717,6 +15211,18 @@
           <t xml:space="preserve">  Hospitality  ·  1 staff</t>
         </is>
       </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="18" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -15112,6 +15618,18 @@
           <t xml:space="preserve">  HR  ·  4 staff</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="18" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -15926,6 +16444,18 @@
           <t xml:space="preserve">  Coffee Shop  ·  3 staff</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="18" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -16076,6 +16606,18 @@
           <t xml:space="preserve">  IT  ·  3 staff</t>
         </is>
       </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="18" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -16238,6 +16780,18 @@
           <t xml:space="preserve">  Leadership  ·  1 staff</t>
         </is>
       </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="18" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -16399,6 +16953,18 @@
           <t xml:space="preserve">  Cleaning  ·  3 staff</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="18" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -16557,6 +17123,18 @@
           <t xml:space="preserve">  Electrical  ·  2 staff</t>
         </is>
       </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="18" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -16670,6 +17248,18 @@
           <t xml:space="preserve">  Facility Management  ·  2 staff</t>
         </is>
       </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="18" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -16787,6 +17377,18 @@
           <t xml:space="preserve">  Gardening  ·  2 staff</t>
         </is>
       </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="18" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -16896,6 +17498,18 @@
           <t xml:space="preserve">  Maintenance  ·  4 staff</t>
         </is>
       </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="17" t="n"/>
+      <c r="L15" s="17" t="n"/>
+      <c r="M15" s="18" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -17111,6 +17725,18 @@
           <t xml:space="preserve">  Security  ·  5 staff</t>
         </is>
       </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
+      <c r="J20" s="17" t="n"/>
+      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="17" t="n"/>
+      <c r="M20" s="18" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -17371,6 +17997,18 @@
           <t xml:space="preserve">  Property  ·  1 staff</t>
         </is>
       </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="17" t="n"/>
+      <c r="L26" s="17" t="n"/>
+      <c r="M26" s="18" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="n">
